--- a/data/trans_orig/P79_n_R3-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79_n_R3-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>17154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25420</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>500</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30382</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>21450</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>302140</t>
+          <t>310510</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>280626</t>
+          <t>299318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>308816</t>
+          <t>315560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>282716</t>
+          <t>309615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>264148</t>
+          <t>297312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>288229</t>
+          <t>314005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>584855</t>
+          <t>620126</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>563531</t>
+          <t>607061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>594725</t>
+          <t>627544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1523</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30035</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6458</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>22456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>26621</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>17216</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41913</t>
+          <t>43584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37224</t>
+          <t>38728</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55461</t>
+          <t>59108</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27959</t>
+          <t>29941</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38196</t>
+          <t>40451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>65183</t>
+          <t>68670</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47630</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85829</t>
+          <t>86924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>461153</t>
+          <t>472222</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>438862</t>
+          <t>449822</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>478133</t>
+          <t>488633</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>471398</t>
+          <t>499199</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>457385</t>
+          <t>486303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>480390</t>
+          <t>510400</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>932551</t>
+          <t>971421</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>907150</t>
+          <t>947895</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>953882</t>
+          <t>992197</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>11162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10034</t>
+          <t>9490</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6607</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6853</t>
+          <t>8772</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8435</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14343</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>24988</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32201</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>300797</t>
+          <t>297937</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>290813</t>
+          <t>286966</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>306761</t>
+          <t>304682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>326321</t>
+          <t>333314</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>316496</t>
+          <t>323549</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>333318</t>
+          <t>340760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>627118</t>
+          <t>631253</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>614076</t>
+          <t>619035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>637408</t>
+          <t>641281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11199</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23669</t>
+          <t>25394</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>13641</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>7289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23768</t>
+          <t>28140</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>28295</t>
+          <t>39354</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17327</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45883</t>
+          <t>61957</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19993</t>
+          <t>26340</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11106</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30297</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>48287</t>
+          <t>65694</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33247</t>
+          <t>48324</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>88328</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>280025</t>
+          <t>328273</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>261498</t>
+          <t>305031</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>291378</t>
+          <t>343410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>443462</t>
+          <t>382458</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>426754</t>
+          <t>367350</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>457017</t>
+          <t>392560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>723487</t>
+          <t>710732</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>702274</t>
+          <t>687259</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>742138</t>
+          <t>731423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1844</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>386</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>464</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3159,12 +3159,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1598</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>461</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8898</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -3340,27 +3340,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>176331</t>
+          <t>203028</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>172412</t>
+          <t>198782</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>178216</t>
+          <t>205060</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>254866</t>
+          <t>223586</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>250293</t>
+          <t>218871</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257027</t>
+          <t>226191</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>431197</t>
+          <t>426613</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>426366</t>
+          <t>420466</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>434378</t>
+          <t>429971</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>822</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4492</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>876</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,67 +3718,67 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11994</t>
+          <t>12437</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>9791</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>5010</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>16646</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>7342</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>3785</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>12982</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>26643</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>258649</t>
+          <t>255783</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>250542</t>
+          <t>247527</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>263723</t>
+          <t>261603</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>243272</t>
+          <t>247458</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>235905</t>
+          <t>239185</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>248678</t>
+          <t>253316</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>501921</t>
+          <t>503240</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>491709</t>
+          <t>491776</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>508988</t>
+          <t>511584</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>3672</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5418</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>10566</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>17325</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>16894</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20429</t>
+          <t>26124</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>24633</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>31417</t>
+          <t>37713</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>49754</t>
+          <t>60142</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>46733</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>71158</t>
+          <t>76918</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>69685</t>
+          <t>84775</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>67030</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>105969</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>596955</t>
+          <t>686660</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>583965</t>
+          <t>673438</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>606056</t>
+          <t>697230</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>791042</t>
+          <t>697678</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>768373</t>
+          <t>679870</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>824491</t>
+          <t>712155</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1387997</t>
+          <t>1384338</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1363433</t>
+          <t>1361381</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1418956</t>
+          <t>1404095</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12147</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>76433</t>
+          <t>91726</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>74819</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>111365</t>
+          <t>112075</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>69705</t>
+          <t>81857</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>56188</t>
+          <t>66839</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>85430</t>
+          <t>100500</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>146138</t>
+          <t>173583</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>150266</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>180072</t>
+          <t>198283</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>174378</t>
+          <t>203717</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>82226</t>
+          <t>180204</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>245173</t>
+          <t>229424</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>192156</t>
+          <t>220844</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>171610</t>
+          <t>199724</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>212138</t>
+          <t>244373</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>366534</t>
+          <t>424562</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>218781</t>
+          <t>390681</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>442118</t>
+          <t>459484</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>673537</t>
+          <t>497161</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>570950</t>
+          <t>468964</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>813727</t>
+          <t>523840</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,22 +5082,22 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>452392</t>
+          <t>524809</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>431052</t>
+          <t>499314</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>476064</t>
+          <t>549097</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>1125930</t>
+          <t>1021969</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1022105</t>
+          <t>982539</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1328726</t>
+          <t>1059545</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12120</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>36691</t>
+          <t>36819</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>20614</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>42789</t>
+          <t>44916</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>66446</t>
+          <t>62666</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>123153</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>78830</t>
+          <t>101307</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>129856</t>
+          <t>150312</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>129808</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>85867</t>
+          <t>111519</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>132514</t>
+          <t>153597</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>213650</t>
+          <t>252961</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>178767</t>
+          <t>220220</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>248984</t>
+          <t>285372</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>284135</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>227212</t>
+          <t>296308</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>328963</t>
+          <t>371703</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>316467</t>
+          <t>367642</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>258908</t>
+          <t>334313</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>353173</t>
+          <t>401881</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>600602</t>
+          <t>702147</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>516364</t>
+          <t>646586</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>661283</t>
+          <t>752580</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>3049587</t>
+          <t>3051574</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2992170</t>
+          <t>3000343</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3137027</t>
+          <t>3096532</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3265469</t>
+          <t>3218118</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3217920</t>
+          <t>3176703</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3349284</t>
+          <t>3255797</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>6315056</t>
+          <t>6269692</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6237420</t>
+          <t>6207759</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6439604</t>
+          <t>6331232</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
